--- a/AAII_Financials/Quarterly/PRGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRGO_QTR_FIN.xlsx
@@ -656,539 +656,552 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E7" s="2">
         <v>46109</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45563</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45108</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44835</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44744</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44653</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44471</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44380</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44289</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44009</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43918</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43736</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43645</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43554</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43372</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42917</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42826</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1022800</v>
+      </c>
+      <c r="E8" s="3">
         <v>969200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1109600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1043300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1056300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1043900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1138300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1087500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1065500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1082100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1156900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1123800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1193100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1181700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1155300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1100200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1121700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1074500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1104900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1042700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>981100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1010000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1053200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1003000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>948800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1341000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1322800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1191100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1149000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1174500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1195200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1133100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1186400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1217000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1283100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1231300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1237900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1194000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1331300</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1261600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>708900</v>
+      </c>
+      <c r="E9" s="3">
         <v>643700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>747400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>666200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>693400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>651600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>752400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>683100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>670800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>724400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>729600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>712600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>765100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>767900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>772700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>737300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>749600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>736700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>742500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>706300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>632100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>641600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>668800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>633300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>601600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>857800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>842000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>778300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>718200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>725700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>752200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>708300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>715400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>724300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>770300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>733500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>733300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>729600</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>843600</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>777100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>313900</v>
+      </c>
+      <c r="E10" s="3">
         <v>325500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>362200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>377100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>362900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>392300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>385900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>404400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>394700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>357700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>427300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>411200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>428000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>413800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>382600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>362900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>372100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>337800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>362400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>336400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>349000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>368400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>384400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>369700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>347200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>483200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>480800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>412800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>430800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>448800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>443000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>424800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>471000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>492700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>512800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>497800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>504600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>464400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>487700</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>484500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1231,130 +1244,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E12" s="3">
         <v>24600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>21800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>24900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>22000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>26700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>27800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>29000</v>
-      </c>
-      <c r="M12" s="3">
-        <v>29600</v>
       </c>
       <c r="N12" s="3">
         <v>29600</v>
       </c>
       <c r="O12" s="3">
+        <v>29600</v>
+      </c>
+      <c r="P12" s="3">
         <v>32200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>31100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>32600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>29800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>31500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>29300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>30300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>27600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>33000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>31100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>33000</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>30400</v>
       </c>
       <c r="AA12" s="3">
         <v>30400</v>
       </c>
       <c r="AB12" s="3">
+        <v>30400</v>
+      </c>
+      <c r="AC12" s="3">
         <v>41900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>59400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>44000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>43900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>40200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>44600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>43700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>91900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>38400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>46900</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>38400</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>42600</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>39800</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>41500</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1475,175 +1492,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="E14" s="3">
         <v>407300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1400400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>20800</v>
       </c>
-      <c r="G14" s="3">
-        <v>23700</v>
-      </c>
       <c r="H14" s="3">
+        <v>11700</v>
+      </c>
+      <c r="I14" s="3">
         <v>32400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>22500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>38100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>71000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>78400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>103600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>15500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>13300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>19300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>55100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>11900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>16100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>33600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>170000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>11000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>6100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>20900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>3300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>142100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>28800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>42200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>13400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>239800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>5400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>2000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>6400</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>11600</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>174700</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>50900</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>615300</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>1621700</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E15" s="3">
         <v>83300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>85900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>85400</v>
       </c>
-      <c r="G15" s="3">
-        <v>86300</v>
-      </c>
       <c r="H15" s="3">
+        <v>81800</v>
+      </c>
+      <c r="I15" s="3">
         <v>79900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>80300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>82300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>81900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>81400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>85900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>91000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>93900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>88700</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1719,8 +1742,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1760,252 +1786,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>983500</v>
+      </c>
+      <c r="E17" s="3">
         <v>935600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>996400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>949700</v>
       </c>
-      <c r="G17" s="3">
-        <v>988400</v>
-      </c>
       <c r="H17" s="3">
+        <v>1000400</v>
+      </c>
+      <c r="I17" s="3">
         <v>964500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>999500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>974000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1020500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1058300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1062700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1045900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1129100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1129000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1124300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1066700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1137900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1056300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1058200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>604400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1107000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>958600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1015600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>944500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>886100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1195300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1329700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1136900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1094000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1072200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1087700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1255100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1091700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1061200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1124500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1068900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1224300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1065500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1815900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2730600</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E18" s="3">
         <v>33600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>113200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>93600</v>
       </c>
-      <c r="G18" s="3">
-        <v>67900</v>
-      </c>
       <c r="H18" s="3">
+        <v>55900</v>
+      </c>
+      <c r="I18" s="3">
         <v>79400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>138800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>113500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>45000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>23800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>94200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>77900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>64000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>52700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>31000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>33500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-16200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>18200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>46700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>438300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-125900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>51400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>37600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>58500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>62700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>145700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>54200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>55000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>102300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>107500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-122000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>94700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>155800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>158600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>162400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>13600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>128500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-484600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>-1469000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2048,296 +2081,303 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-14100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-8300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-9700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-10900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-15600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-45300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-37000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-92100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-31200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-36800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-49400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-31200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-34400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-153000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-47200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-31000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-27300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>43100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-28000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-21400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>96200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>43000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-39400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-45300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-26700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-33700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-89900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-32700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-1159300</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-433000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>115400</v>
+      </c>
+      <c r="E21" s="3">
         <v>131000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>207400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>178700</v>
       </c>
-      <c r="G21" s="3">
-        <v>162300</v>
-      </c>
       <c r="H21" s="3">
+        <v>145800</v>
+      </c>
+      <c r="I21" s="3">
         <v>169000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>223700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>206700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>129800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>111500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>183900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>177200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>173500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>134300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>82800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>85000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-24800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>56500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>83300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>462400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-82200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>107400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>145300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>110200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>207800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>68800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>199300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>121900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>177500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>303300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>27200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>163600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>220000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>243600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>241000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>35100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>205200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>-1525300</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>-1787300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E22" s="3">
         <v>49000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>52800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>50100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>49100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>48400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>50900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>64500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>50900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>50300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>48700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>51500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>50400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>37800</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>17</v>
@@ -2345,8 +2385,8 @@
       <c r="S22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -2396,8 +2436,8 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
-      <c r="AK22" s="3" t="s">
-        <v>17</v>
+      <c r="AK22" s="3">
+        <v>0</v>
       </c>
       <c r="AL22" s="3" t="s">
         <v>17</v>
@@ -2414,252 +2454,261 @@
       <c r="AP22" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="AQ22" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>105500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-408600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1331700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>70000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>21800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-74000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-98600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-54300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>19200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>22500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-14300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-108300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-13000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>9900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>388900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-157100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>17000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-115400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>48400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>15500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>114700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-34200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>97300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>27000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>80900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>203700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-79000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>55300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>110500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>131900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>128700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-76300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>95800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-1643900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-1902000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-18700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>82900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>111500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>39400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>31700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-102700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-26600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>13600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>48600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-43400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-11700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-22200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>442800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-45200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>14200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-63200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>22000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>8300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-15200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>18000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>17000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>122300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-11500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>19100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>29700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>43600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>84200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-6700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>24200</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-284800</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-311800</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2780,252 +2829,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>88600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-389900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1414600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-41500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-105700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-27700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>15400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-12700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-52100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-64900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>32100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-53900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-111900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-52200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>26400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>12400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>106400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>92200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>9000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>63900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>81400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-67500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>36200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>80800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>88300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>44500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-69600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>71600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-1359100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-1590200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-398600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1418100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-44500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-21000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-108400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-32300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>14200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>8400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-12700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-52100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-64900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>32100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-53900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-111900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-52200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>26400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>12400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>106400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>92200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>9000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>63900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>81400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-67500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>36200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>80800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>88300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>44500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-69600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>71600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-1359100</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-1590200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3146,85 +3204,88 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E29" s="3">
         <v>-8700</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-3500</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-5200</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-7900</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-6500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-3000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-3400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-2700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-2100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-4600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-1200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-11000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>2700</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-1100</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-22500</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-5000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>54200</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>35300</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-122800</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-181000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>48200</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>17</v>
@@ -3250,11 +3311,11 @@
       <c r="AJ29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-15100</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>17</v>
@@ -3268,8 +3329,11 @@
       <c r="AP29" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3390,8 +3454,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3512,252 +3579,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
         <v>14100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>8300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>9700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>10900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>15600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>45300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>37000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>92100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>31200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>36800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>49400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>31200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>34400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>153000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>10100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>47200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>31000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>27300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-43100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>28000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>21400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-96200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-43000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>39400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>45300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>26700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>33700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>89900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>32700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>1159300</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>433000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-398600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1418100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-44500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-21000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-108400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-32300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>14200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>8400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-23700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-49400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-65100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>9600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-58900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-57700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>38100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-175000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-154600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>60600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>106400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>92200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>9000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>63900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>81400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-67500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>36200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>80800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>73200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>44500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-69600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>71600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-1359100</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-1590200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3878,257 +3954,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-398600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1418100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-44500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-21000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-108400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-32300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>14200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>8400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-23700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-49400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-65100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>9600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-58900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-57700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>38100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-175000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-154600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>60600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>106400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>92200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>9000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>63900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>81400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-67500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>36200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>80800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>73200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>44500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-69600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>71600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-1359100</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-1590200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E38" s="2">
         <v>46109</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45563</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45108</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45017</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44835</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44744</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44653</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44471</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44380</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44289</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44009</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43918</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43736</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43645</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43554</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43372</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42917</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42826</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4171,8 +4256,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4215,130 +4301,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>399700</v>
+      </c>
+      <c r="E41" s="3">
         <v>357200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>531600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>432100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>454200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>409900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>558800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1462400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>542800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>658500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>744300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>598300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>555200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>553000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>600700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>468700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>485300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1965500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1864900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2078100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>317500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>470900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>641500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>849400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1456300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>510400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>354300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>398500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1055700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>837900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>551100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>444200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>526500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>687300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>678700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>775900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>760800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3077800</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>622300</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>362700</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4370,632 +4460,647 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N42" s="3">
         <v>100</v>
       </c>
       <c r="O42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="3">
         <v>100</v>
       </c>
       <c r="R42" s="3">
+        <v>100</v>
+      </c>
+      <c r="S42" s="3">
         <v>200</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
       <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
         <v>200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>4100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>6600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>3700</v>
-      </c>
-      <c r="AG42" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="AH42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AI42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>3400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>4100</v>
-      </c>
-      <c r="AL42" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="AM42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AN42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO42" s="3">
         <v>3500</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>700</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>750000</v>
+      </c>
+      <c r="E43" s="3">
         <v>732800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>650100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>675600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>706600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>755000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>686200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>813300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>751600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>805700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>768100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>761400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>779900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>770400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>738600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>739500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>777100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>711800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>693100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>728400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>642600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>659400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1073900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1118900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1023900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1324800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1269500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1128000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1133700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1136800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1073100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1079800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1129800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1123400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1130800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1076600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1065900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1050200</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1176000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1124100</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1064500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1121400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1149000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1227000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1215500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1155000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1081800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1133800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1116200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1121300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1140900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1149500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1167500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1183000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1150300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1085200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1079600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1022400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1020200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1092500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1115900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1136100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1200200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1100700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1034700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>930800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>967300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>990500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>940500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>912900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>878000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>885300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>883800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>843800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>806900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>821900</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>818100</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>800200</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>795000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>884600</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E45" s="3">
         <v>305300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>301900</v>
       </c>
       <c r="F45" s="3">
         <v>301900</v>
       </c>
       <c r="G45" s="3">
+        <v>301900</v>
+      </c>
+      <c r="H45" s="3">
         <v>24900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>35300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>294200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>27100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>37700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>37900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>39900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>230200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>289700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>309500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>235600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>281300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>325400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2342600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2219300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>215400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>326000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>284500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>276500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>159200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>220200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>302700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>118000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>400000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>359500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>236300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>242800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>199100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>297400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>176500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>181700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>211300</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>249200</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2451700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2712400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2797400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2879200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2615000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2533000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2481900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3707800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2959100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2806400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2832900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2765300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2773000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2740700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2719900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2583300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2651500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3935500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3859900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4225900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4420200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4488600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3133500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3398300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3803500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3046200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2756900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2739800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3435400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3009300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2902200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2768800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2778500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2900700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2819600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2971800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2821300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>5113400</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>2805300</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2622000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E47" s="3">
         <v>27200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>25400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>57500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>61300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>63400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>67400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>60200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>78000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>109800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>91900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>133600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>117700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>89300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>63400</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>17</v>
@@ -5003,44 +5108,44 @@
       <c r="T47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="V47" s="3">
         <v>68200</v>
-      </c>
-      <c r="V47" s="3">
-        <v>70800</v>
       </c>
       <c r="W47" s="3">
         <v>70800</v>
       </c>
       <c r="X47" s="3">
+        <v>70800</v>
+      </c>
+      <c r="Y47" s="3">
         <v>70600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>71700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>71300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>72800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>20800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>20100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>19500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>19600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>19500</v>
-      </c>
-      <c r="AG47" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="AH47" s="3" t="s">
         <v>17</v>
@@ -5051,8 +5156,8 @@
       <c r="AJ47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AK47" s="3">
-        <v>0</v>
+      <c r="AK47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AL47" s="3">
         <v>0</v>
@@ -5069,252 +5174,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1015100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1050600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1078000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1083700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1097700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1094500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1104700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1103500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1112800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1101500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1113700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1122200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1145600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1152000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1165400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1072400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1071800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1068200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1058900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1042900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1036100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1041900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1213000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1080200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1056700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1041000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1060300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1030500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>976800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>977800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>829100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>820200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>811900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>829300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>833100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>822300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>876900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>875300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>870100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>881300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3887800</v>
+      </c>
+      <c r="E49" s="3">
         <v>3965700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4406200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5765900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6042700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5837200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5749100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6082200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6008400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6368400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6515200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6496100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6688600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6734300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6779200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6495300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6805200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5029600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5150800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5263100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5376900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5425600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6758200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6749500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6926300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7023900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7106700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7169000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>6643000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6756900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>6888000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>7001300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>7293100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>7559900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>7556200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>7602800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>7626400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>7519400</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>9910700</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>12031800</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5435,8 +5549,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5557,130 +5674,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>224500</v>
+      </c>
+      <c r="E52" s="3">
         <v>222700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>224900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>233500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>229300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>226300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>239500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>227100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>225200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>226200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>229600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>234300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>233500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>232500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>289400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>526500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>391100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>356200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>287900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>313200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>326300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>298100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>312000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>276700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>269000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>268800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>357400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>352000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>353900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>356000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>364100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>352600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>342100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>349700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>419900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>445700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>467600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>471300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>284000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>353000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5801,130 +5924,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7609500</v>
+      </c>
+      <c r="E54" s="3">
         <v>7983300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8535200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10084000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10094100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9759800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9647700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11203200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10397300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10640300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10809100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10758300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10964700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10954900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11017300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10677500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10919600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10389500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10425700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10915900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>11230300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>11324800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>11488400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11576000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12128300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11400700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11301400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11310800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11428700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11119500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>10983400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>10942900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>11225600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>11639600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>11628800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>11842600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>11792200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>13979400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>13870100</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>15888100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5967,8 +6096,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6011,740 +6141,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400400</v>
+      </c>
+      <c r="E57" s="3">
         <v>434800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>474500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>469700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>489000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>502300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>495200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>458500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>471500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>453700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>477700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>433100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>470500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>505200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>537300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>461400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>490400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>479600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>411200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>405600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>402400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>430300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>543800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>536400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>489100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>555800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>520200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>524900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>513700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>549200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>474900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>503600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>533400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>512200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>450200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>477100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>480800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>476300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>471700</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>502900</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E58" s="3">
         <v>37500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>62300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>65000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>65300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>63700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>64200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>470700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>469800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>467200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>468100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>66000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>66700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>67100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>36200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>33500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>30800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>603800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>629400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>630100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>35800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>37800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>16500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>606500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>287800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>398800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>467900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>190200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>194200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>197700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>58000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>70400</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>417100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>406900</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1175400</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>572800</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>265000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>206900</v>
+      </c>
+      <c r="E59" s="3">
         <v>134900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>121100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>232400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>190700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>139200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>99800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>63800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>104300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>170200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>186800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>175000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>214700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>199600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>540100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>520100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>493400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>497100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>572900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>968800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>952000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>980700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>800400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>783400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>764100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>791400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>812200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>796700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>878300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>814800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>872300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>795700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>806500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>822300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>915400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>838300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>742000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>833500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>791800</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>744900</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1054800</v>
+      </c>
+      <c r="E60" s="3">
         <v>997600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1012900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1145300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1126100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1073800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1044200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1450500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1488100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1554500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1586300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1008400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1056900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1086800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1113600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1015000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1014600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>981300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1587900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2003800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1984500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1446800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1382000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1336300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1859700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1635000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1335800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1324700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1790800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1831900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1537400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1493500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1537600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1392500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1436000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1732500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1629700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2485200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1836300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1512800</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3439600</v>
+      </c>
+      <c r="E61" s="3">
         <v>3791200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3787900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3795400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3802100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3771600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3758100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4517900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3792200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3782100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3804100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4221500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4236200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4247500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4070400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4077500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4086100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3510600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2916700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2920900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2925800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3525300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3528300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3543600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3536000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3182900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3365800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3361500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3084400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2749900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3052200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3071000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3085300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3280600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3270800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3275700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3267900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>4618900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>5224500</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>5638000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>452600</v>
+      </c>
+      <c r="E62" s="3">
         <v>542200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>602600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>502400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>486800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>361200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>295400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>455000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>360000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>369000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>358200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>440900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>478400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>452900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>991200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>982300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>969100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>793100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>769400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>808800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>808900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>794700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>923000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>875700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>821700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>795900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>795700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>865500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>827100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>836900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>725700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>718400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>705400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>760900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>751400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>792600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>813400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>808000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>851700</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1254700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6865,8 +7014,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6987,8 +7139,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7109,130 +7264,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5093700</v>
+      </c>
+      <c r="E66" s="3">
         <v>5484500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5599700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5637500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5621800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5395800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5328300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6637200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5852000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5953300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6041200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6020200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6116100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6121000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6175200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6074800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6069800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5285000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5274000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5733500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5719200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5766800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5833300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5755700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6217900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5614300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5497600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5552000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5702500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5418900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5315400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5283100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5328500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5434200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>5458300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>5800900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>5711000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>7911600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>7912000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>8404900</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7275,8 +7436,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7397,8 +7559,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7519,8 +7684,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7641,8 +7809,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7763,130 +7934,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-4001900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-4076300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3677500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2259400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2266900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2258500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2252100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2207700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2186700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2078300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2080300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2048000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2062200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2070600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2067600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2043900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1994500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1929400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1927000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1936600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1877700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1820000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1858100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1683100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1528500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1589100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1695500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1676600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-1768800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-1777800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-1838300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-1919700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-1852200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-1888400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-1975500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-2049600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-2094000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-2024000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-2095100</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-736900</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8007,8 +8184,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8129,8 +8309,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8251,130 +8434,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2515800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2498800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2935500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4446500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4472300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4364000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4319400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4566000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4545300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4687000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4767900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4738100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4848600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4833900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4842100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4602700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4849800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5104500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5151700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5182400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5511100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5558000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5655100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5820300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5910400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5786400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5803800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5758800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5726200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5700600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5668000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5659800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5897100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6205400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6170500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6041700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6081200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>6067800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>5958100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>7483200</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8495,257 +8684,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E80" s="2">
         <v>46109</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45563</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45108</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45017</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44835</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44744</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44653</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44471</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44380</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44289</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44009</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43918</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43736</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43645</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43554</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43372</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42917</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42826</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-398600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1418100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-44500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-21000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-108400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-32300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>14200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>8400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-23700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-49400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-65100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>9600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-58900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-57700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>38100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-175000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-154600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>60600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>106400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>92200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>9000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>63900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>81400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-67500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>36200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>80800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>73200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>44500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-69600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>71600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-1359100</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-1590200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8788,130 +8986,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E83" s="3">
         <v>25100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>25200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>24800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>24400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>23000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>22800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>23000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>24600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>23500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20600</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>21000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>97100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>88500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>83500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>69500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>73400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>73500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>74900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>90400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>100100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>96900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>94700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>93100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>103000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>102000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>94900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>96600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>99600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>106200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>108300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>109500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>111700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>112300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>111400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>109400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>118600</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>114700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9032,8 +9234,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9154,8 +9359,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9276,8 +9484,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9398,8 +9609,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9520,130 +9734,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>82600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-113600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>175400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>51700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>75900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-64500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>312600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>42200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>208700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>124500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>52900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>19400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>185900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>59200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-16900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>79100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-105400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>343800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-82300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>110400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>63100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>290900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>171800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>89500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>140000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>63800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>94500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>194300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>144000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>82300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>172400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>216900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>196700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>90800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>194500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>206200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>219000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9686,130 +9906,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-26800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-21900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-19200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-27000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-51000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-27100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-28400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-25100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-31800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-20000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-21600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-38400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-20300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-41700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-42000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-23000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-45400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-32700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-51500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-51200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-13900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-21100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-19900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-13400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-33400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-15200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-21600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-92600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9930,8 +10154,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10052,130 +10279,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>349400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-24500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-25700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-37100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>212700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-73300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-23500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-30700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-19600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-26000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-20900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1974400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>62700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-41900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1453500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-21800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-114000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-127500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-38600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>53100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-74800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-106300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-651800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-68100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>230100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-46100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-51500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-27100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>66000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-5800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>2287800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>94500</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>38400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10218,13 +10451,14 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>39900</v>
+        <v>40200</v>
       </c>
       <c r="E96" s="3">
         <v>39900</v>
@@ -10233,115 +10467,118 @@
         <v>39900</v>
       </c>
       <c r="G96" s="3">
+        <v>39900</v>
+      </c>
+      <c r="H96" s="3">
         <v>38900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>40600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>39600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>37600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>37700</v>
-      </c>
-      <c r="L96" s="3">
-        <v>37600</v>
       </c>
       <c r="M96" s="3">
         <v>37600</v>
       </c>
       <c r="N96" s="3">
+        <v>37600</v>
+      </c>
+      <c r="O96" s="3">
         <v>38900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>37000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>36200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-35400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-37400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-35400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-34200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-31800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-32700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-32500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-32600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-30900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-31100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-31000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-30900</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-28800</v>
       </c>
       <c r="AD96" s="3">
         <v>-28800</v>
       </c>
       <c r="AE96" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-28900</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-25900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-26200</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-25900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-26100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-26700</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-22400</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-22700</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-23000</v>
       </c>
       <c r="AN96" s="3">
         <v>-23000</v>
       </c>
       <c r="AO96" s="3">
-        <v>-20800</v>
+        <v>-23000</v>
       </c>
       <c r="AP96" s="3">
         <v>-20800</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-20800</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10462,8 +10699,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10584,8 +10824,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10706,370 +10949,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-388900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-45300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-54400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-50300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-54000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-61800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1154100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>653300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-49800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-60400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-44600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-43300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-48600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-50700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-42500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-43000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>559000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-51900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-58000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-36300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-41100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-43300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-201400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-646500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>602100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>64700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-31500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-144900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>219800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-41600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-34300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-175400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-199600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-162600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-383700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-172500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2411300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-37200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-34600</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-539600</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E101" s="3">
         <v>10300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-26100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>12500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-7500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>11700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-7400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>14600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-11900</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>14600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-11900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-47900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-8800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>10600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>15100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-16400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>3600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>9300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>10400</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-6500</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-174400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>99500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-19800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>37100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-141700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-904700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>920700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-115700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-92800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>153000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>43100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-47700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>132000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-16600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1480200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>86200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-208900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1752200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-144500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-161000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-207900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-606900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>945900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>156100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-44200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-657200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>217800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>286800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>106900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-82300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-160800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>8600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-97200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>15100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-2317000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>2455500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>259600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-279100</v>
       </c>
     </row>
